--- a/uploadedFiles/Questionnaire/2014 Site Survey Questionnaire Final Reviewed 2.xlsx
+++ b/uploadedFiles/Questionnaire/2014 Site Survey Questionnaire Final Reviewed 2.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\john\Desktop\coders\deborah\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\john\Desktop\hs3MVC_Latest\Generic\uploadedFiles\Questionnaire\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="452" uniqueCount="147">
   <si>
     <t>Page</t>
   </si>
@@ -227,42 +227,9 @@
     <t>Y/N</t>
   </si>
   <si>
-    <t>1001= 0&amp;1001=0:1005</t>
-  </si>
-  <si>
     <t/>
   </si>
   <si>
-    <t>1003= 0&amp;1003=0:1005</t>
-  </si>
-  <si>
-    <t>1005= 0&amp;1005=0:1008</t>
-  </si>
-  <si>
-    <t>1009= 0&amp;1009=0:1011</t>
-  </si>
-  <si>
-    <t>1011= 0&amp;1011=0:1013</t>
-  </si>
-  <si>
-    <t>1014= 0&amp;1014=0:1018</t>
-  </si>
-  <si>
-    <t>1021= 0&amp;1021=0:1024</t>
-  </si>
-  <si>
-    <t>1025= 0&amp;1025=0:1028</t>
-  </si>
-  <si>
-    <t>1029= 0&amp;1029=0:1031</t>
-  </si>
-  <si>
-    <t>1031= 0&amp;1031=0:1034</t>
-  </si>
-  <si>
-    <t>1034= 0&amp;1034=0:1036</t>
-  </si>
-  <si>
     <t>FCL or FTL</t>
   </si>
   <si>
@@ -413,17 +380,104 @@
     <t>Site</t>
   </si>
   <si>
-    <t>Certification</t>
-  </si>
-  <si>
-    <t>&lt;b&gt;&lt;i&gt;Overall Certification&lt;/i&gt;&lt;/b&gt; I hereby certify that the information provided here is true and correct and shall be valid for the current calendar year. If any changes to the above occur, I will immediately notify the appropriate point of contact at Honeywell, in writing, regarding its change in status.</t>
+    <t>1001=0&amp;1001=0:1005;</t>
+  </si>
+  <si>
+    <t>1003=0&amp;1003=0:1005;</t>
+  </si>
+  <si>
+    <t>1005=0&amp;1005=0:1008;</t>
+  </si>
+  <si>
+    <t>1009=0&amp;1009=0:1011;</t>
+  </si>
+  <si>
+    <t>1011=0&amp;1011=0:1013;</t>
+  </si>
+  <si>
+    <t>1014=0&amp;1014=0:1018;</t>
+  </si>
+  <si>
+    <t>1021=0&amp;1021=0:1024;</t>
+  </si>
+  <si>
+    <t>1025=0&amp;1025=0:1028;</t>
+  </si>
+  <si>
+    <t>1029=0&amp;1029=0:1031;</t>
+  </si>
+  <si>
+    <t>1031=0&amp;1031=0:1031</t>
+  </si>
+  <si>
+    <t>1034=0&amp;1034=0:1036;</t>
+  </si>
+  <si>
+    <t>Is your site located in the United States?</t>
+  </si>
+  <si>
+    <t>1036=1&amp;1036=1:1036;</t>
+  </si>
+  <si>
+    <t>Does your site ship goods into the United States?</t>
+  </si>
+  <si>
+    <t>1037=0&amp;1037=0:1037;</t>
+  </si>
+  <si>
+    <t>U.S. Location</t>
+  </si>
+  <si>
+    <t>ShipToUS</t>
+  </si>
+  <si>
+    <t>Shipping Method</t>
+  </si>
+  <si>
+    <t>Does your site ship goods into the United States via &lt;p&gt;Full Truck Load&lt;/p&gt;?</t>
+  </si>
+  <si>
+    <t>Full Container Load?</t>
+  </si>
+  <si>
+    <t>Air Freight?</t>
+  </si>
+  <si>
+    <t>Partial Container Load?</t>
+  </si>
+  <si>
+    <t>Package Freight, i.e. FedEx, UPS, DHL, etc.?</t>
+  </si>
+  <si>
+    <t>Other?</t>
+  </si>
+  <si>
+    <t>FullTruckLoad</t>
+  </si>
+  <si>
+    <t>FullContainerLoad</t>
+  </si>
+  <si>
+    <t>AirFreight</t>
+  </si>
+  <si>
+    <t>PartialContainerLoad</t>
+  </si>
+  <si>
+    <t>PackageFreight</t>
+  </si>
+  <si>
+    <t>Other</t>
+  </si>
+  <si>
+    <t>Please Specify:</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="14">
+  <fonts count="13">
     <font>
       <sz val="10"/>
       <name val="宋体"/>
@@ -490,23 +544,17 @@
       <family val="1"/>
     </font>
     <font>
-      <b/>
       <sz val="10"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF262626"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
-      <sz val="9"/>
+      <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF262626"/>
-      <name val="Arial"/>
-      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="7">
@@ -602,7 +650,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
@@ -681,9 +729,6 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -693,22 +738,19 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1103,7 +1145,7 @@
     <col min="2" max="2" width="8.5703125" style="12" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="28.42578125" style="25" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="16.85546875" style="15" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="29.85546875" style="25" customWidth="1"/>
+    <col min="5" max="5" width="38.28515625" style="25" customWidth="1"/>
     <col min="6" max="6" width="9.7109375" style="15" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12" style="15" customWidth="1"/>
     <col min="8" max="8" width="12.5703125" style="22" customWidth="1"/>
@@ -1120,7 +1162,7 @@
     <col min="19" max="19" width="17" style="12" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="29.140625" style="12" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="24.28515625" style="12" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="16.5703125" style="12" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="17.85546875" style="12" bestFit="1" customWidth="1"/>
     <col min="23" max="16384" width="10.28515625" style="12"/>
   </cols>
   <sheetData>
@@ -1197,10 +1239,10 @@
       <c r="X1" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="Y1" s="29" t="s">
+      <c r="Y1" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="Z1" s="29" t="s">
+      <c r="Z1" s="28" t="s">
         <v>27</v>
       </c>
     </row>
@@ -1212,25 +1254,25 @@
         <v>1</v>
       </c>
       <c r="C2" s="14" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="D2" s="15" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="F2" s="16" t="s">
         <v>64</v>
       </c>
       <c r="G2" s="16" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="H2" s="17" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="I2" s="18" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="J2" s="18">
         <f>LEN(E2)</f>
@@ -1254,13 +1296,13 @@
       </c>
       <c r="P2" s="18"/>
       <c r="Q2" s="12" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="R2" s="12" t="s">
-        <v>123</v>
-      </c>
-      <c r="S2" s="30" t="s">
-        <v>65</v>
+        <v>112</v>
+      </c>
+      <c r="S2" s="29" t="s">
+        <v>116</v>
       </c>
       <c r="T2" s="11"/>
       <c r="U2" s="11"/>
@@ -1274,10 +1316,10 @@
         <v>1</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="E3" s="4" t="s">
         <v>30</v>
@@ -1286,20 +1328,20 @@
         <v>64</v>
       </c>
       <c r="G3" s="16" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="H3" s="17" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="I3" s="18" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="J3" s="18">
-        <f t="shared" ref="J3:J37" si="0">LEN(E3)</f>
+        <f t="shared" ref="J3:J40" si="0">LEN(E3)</f>
         <v>121</v>
       </c>
       <c r="K3" s="18">
-        <f t="shared" ref="K3:K37" si="1">LEN(H3)</f>
+        <f t="shared" ref="K3:K40" si="1">LEN(H3)</f>
         <v>19</v>
       </c>
       <c r="L3" s="18">
@@ -1316,10 +1358,10 @@
       </c>
       <c r="P3" s="18"/>
       <c r="Q3" s="12" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="S3" s="11" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="T3" s="11"/>
       <c r="U3" s="11"/>
@@ -1333,10 +1375,10 @@
         <v>1</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>31</v>
@@ -1345,13 +1387,13 @@
         <v>64</v>
       </c>
       <c r="G4" s="16" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="H4" s="17" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="I4" s="18" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="J4" s="18">
         <f t="shared" si="0"/>
@@ -1375,13 +1417,13 @@
       </c>
       <c r="P4" s="18"/>
       <c r="Q4" s="12" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="R4" s="12" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="S4" s="11" t="s">
-        <v>67</v>
+        <v>117</v>
       </c>
       <c r="T4" s="11"/>
       <c r="U4" s="11"/>
@@ -1395,10 +1437,10 @@
         <v>1</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="D5" s="15" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="E5" s="4" t="s">
         <v>32</v>
@@ -1407,13 +1449,13 @@
         <v>64</v>
       </c>
       <c r="G5" s="16" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="H5" s="17" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="I5" s="18" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="J5" s="18">
         <f t="shared" si="0"/>
@@ -1437,10 +1479,10 @@
       </c>
       <c r="P5" s="18"/>
       <c r="Q5" s="12" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="S5" s="11" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="T5" s="11"/>
       <c r="U5" s="11"/>
@@ -1454,10 +1496,10 @@
         <v>2</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="D6" s="15" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="E6" s="4" t="s">
         <v>33</v>
@@ -1466,13 +1508,13 @@
         <v>64</v>
       </c>
       <c r="G6" s="16" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="H6" s="17" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="I6" s="18" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="J6" s="18">
         <f t="shared" si="0"/>
@@ -1496,13 +1538,13 @@
       </c>
       <c r="P6" s="18"/>
       <c r="Q6" s="12" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="R6" s="12" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="S6" s="12" t="s">
-        <v>68</v>
+        <v>118</v>
       </c>
     </row>
     <row r="7" spans="1:26" ht="36">
@@ -1513,10 +1555,10 @@
         <v>2</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="E7" s="4" t="s">
         <v>34</v>
@@ -1525,13 +1567,13 @@
         <v>64</v>
       </c>
       <c r="G7" s="16" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="H7" s="17" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="I7" s="18" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="J7" s="18">
         <f t="shared" si="0"/>
@@ -1555,10 +1597,10 @@
       </c>
       <c r="P7" s="18"/>
       <c r="Q7" s="12" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="S7" s="11" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="T7" s="11"/>
       <c r="U7" s="11"/>
@@ -1572,10 +1614,10 @@
         <v>2</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="D8" s="15" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="E8" s="4" t="s">
         <v>35</v>
@@ -1584,13 +1626,13 @@
         <v>64</v>
       </c>
       <c r="G8" s="16" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="H8" s="17" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="I8" s="18" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="J8" s="18">
         <f t="shared" si="0"/>
@@ -1614,10 +1656,10 @@
       </c>
       <c r="P8" s="18"/>
       <c r="Q8" s="12" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="S8" s="11" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="T8" s="11"/>
       <c r="U8" s="11"/>
@@ -1631,10 +1673,10 @@
         <v>3</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="E9" s="4" t="s">
         <v>36</v>
@@ -1643,13 +1685,13 @@
         <v>64</v>
       </c>
       <c r="G9" s="16" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="H9" s="17" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="I9" s="18" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="J9" s="18">
         <f t="shared" si="0"/>
@@ -1673,10 +1715,10 @@
       </c>
       <c r="P9" s="18"/>
       <c r="Q9" s="12" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="S9" s="11" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="T9" s="11"/>
       <c r="U9" s="11"/>
@@ -1690,10 +1732,10 @@
         <v>4</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="D10" s="15" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="E10" s="4" t="s">
         <v>37</v>
@@ -1702,13 +1744,13 @@
         <v>64</v>
       </c>
       <c r="G10" s="16" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="H10" s="17" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="I10" s="18" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="J10" s="18">
         <f t="shared" si="0"/>
@@ -1732,13 +1774,13 @@
       </c>
       <c r="P10" s="18"/>
       <c r="Q10" s="12" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="R10" s="12" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="S10" s="11" t="s">
-        <v>69</v>
+        <v>119</v>
       </c>
       <c r="T10" s="11"/>
       <c r="U10" s="11"/>
@@ -1752,10 +1794,10 @@
         <v>4</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="E11" s="4" t="s">
         <v>38</v>
@@ -1764,13 +1806,13 @@
         <v>64</v>
       </c>
       <c r="G11" s="16" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="H11" s="17" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="I11" s="18" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="J11" s="18">
         <f t="shared" si="0"/>
@@ -1794,10 +1836,10 @@
       </c>
       <c r="P11" s="18"/>
       <c r="Q11" s="12" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="S11" s="11" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="T11" s="11"/>
       <c r="U11" s="11"/>
@@ -1811,10 +1853,10 @@
         <v>5</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="D12" s="15" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="E12" s="4" t="s">
         <v>39</v>
@@ -1823,13 +1865,13 @@
         <v>64</v>
       </c>
       <c r="G12" s="16" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="H12" s="17" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="I12" s="18" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="J12" s="18">
         <f t="shared" si="0"/>
@@ -1853,13 +1895,13 @@
       </c>
       <c r="P12" s="18"/>
       <c r="Q12" s="12" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="R12" s="12" t="s">
-        <v>123</v>
-      </c>
-      <c r="S12" s="30" t="s">
-        <v>70</v>
+        <v>112</v>
+      </c>
+      <c r="S12" s="29" t="s">
+        <v>120</v>
       </c>
       <c r="T12" s="11"/>
       <c r="U12" s="11"/>
@@ -1873,10 +1915,10 @@
         <v>5</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="D13" s="15" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="E13" s="4" t="s">
         <v>40</v>
@@ -1885,13 +1927,13 @@
         <v>64</v>
       </c>
       <c r="G13" s="16" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="H13" s="17" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="I13" s="18" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="J13" s="18">
         <f t="shared" si="0"/>
@@ -1915,10 +1957,10 @@
       </c>
       <c r="P13" s="18"/>
       <c r="Q13" s="12" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="S13" s="12" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="14" spans="1:26" ht="48">
@@ -1929,10 +1971,10 @@
         <v>5</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="D14" s="15" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="E14" s="4" t="s">
         <v>41</v>
@@ -1941,13 +1983,13 @@
         <v>64</v>
       </c>
       <c r="G14" s="16" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="H14" s="17" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="I14" s="18" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="J14" s="18">
         <f t="shared" si="0"/>
@@ -1971,10 +2013,10 @@
       </c>
       <c r="P14" s="18"/>
       <c r="Q14" s="12" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="S14" s="12" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="15" spans="1:26" ht="36">
@@ -1985,10 +2027,10 @@
         <v>6</v>
       </c>
       <c r="C15" s="21" t="s">
+        <v>104</v>
+      </c>
+      <c r="D15" s="15" t="s">
         <v>115</v>
-      </c>
-      <c r="D15" s="15" t="s">
-        <v>126</v>
       </c>
       <c r="E15" s="4" t="s">
         <v>42</v>
@@ -1997,13 +2039,13 @@
         <v>64</v>
       </c>
       <c r="G15" s="16" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="H15" s="17" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="I15" s="18" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="J15" s="18">
         <f t="shared" si="0"/>
@@ -2027,13 +2069,13 @@
       </c>
       <c r="P15" s="18"/>
       <c r="Q15" s="12" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="R15" s="12" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="S15" s="12" t="s">
-        <v>71</v>
+        <v>121</v>
       </c>
     </row>
     <row r="16" spans="1:26" ht="48">
@@ -2044,10 +2086,10 @@
         <v>6</v>
       </c>
       <c r="C16" s="21" t="s">
+        <v>104</v>
+      </c>
+      <c r="D16" s="15" t="s">
         <v>115</v>
-      </c>
-      <c r="D16" s="15" t="s">
-        <v>126</v>
       </c>
       <c r="E16" s="4" t="s">
         <v>43</v>
@@ -2056,13 +2098,13 @@
         <v>64</v>
       </c>
       <c r="G16" s="16" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="H16" s="17" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="I16" s="18" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="J16" s="18">
         <f t="shared" si="0"/>
@@ -2086,10 +2128,10 @@
       </c>
       <c r="P16" s="18"/>
       <c r="Q16" s="12" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="S16" s="12" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17" spans="1:19" ht="36">
@@ -2100,10 +2142,10 @@
         <v>6</v>
       </c>
       <c r="C17" s="21" t="s">
+        <v>104</v>
+      </c>
+      <c r="D17" s="15" t="s">
         <v>115</v>
-      </c>
-      <c r="D17" s="15" t="s">
-        <v>126</v>
       </c>
       <c r="E17" s="4" t="s">
         <v>44</v>
@@ -2112,13 +2154,13 @@
         <v>64</v>
       </c>
       <c r="G17" s="16" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="H17" s="17" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="I17" s="18" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="J17" s="18">
         <f t="shared" si="0"/>
@@ -2142,10 +2184,10 @@
       </c>
       <c r="P17" s="18"/>
       <c r="Q17" s="12" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="S17" s="12" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="18" spans="1:19" ht="48">
@@ -2156,10 +2198,10 @@
         <v>6</v>
       </c>
       <c r="C18" s="21" t="s">
+        <v>104</v>
+      </c>
+      <c r="D18" s="15" t="s">
         <v>115</v>
-      </c>
-      <c r="D18" s="15" t="s">
-        <v>126</v>
       </c>
       <c r="E18" s="4" t="s">
         <v>45</v>
@@ -2168,13 +2210,13 @@
         <v>64</v>
       </c>
       <c r="G18" s="16" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="H18" s="17" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="I18" s="18" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="J18" s="18">
         <f t="shared" si="0"/>
@@ -2198,10 +2240,10 @@
       </c>
       <c r="P18" s="18"/>
       <c r="Q18" s="12" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="S18" s="12" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="19" spans="1:19" ht="48">
@@ -2212,10 +2254,10 @@
         <v>6</v>
       </c>
       <c r="C19" s="21" t="s">
+        <v>104</v>
+      </c>
+      <c r="D19" s="15" t="s">
         <v>115</v>
-      </c>
-      <c r="D19" s="15" t="s">
-        <v>126</v>
       </c>
       <c r="E19" s="4" t="s">
         <v>46</v>
@@ -2224,13 +2266,13 @@
         <v>64</v>
       </c>
       <c r="G19" s="16" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="H19" s="17" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="I19" s="18" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="J19" s="18">
         <f t="shared" si="0"/>
@@ -2254,10 +2296,10 @@
       </c>
       <c r="P19" s="18"/>
       <c r="Q19" s="12" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="S19" s="12" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="20" spans="1:19" ht="60">
@@ -2268,10 +2310,10 @@
         <v>6</v>
       </c>
       <c r="C20" s="21" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="D20" s="15" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="E20" s="4" t="s">
         <v>47</v>
@@ -2280,13 +2322,13 @@
         <v>64</v>
       </c>
       <c r="G20" s="16" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="H20" s="17" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="I20" s="18" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="J20" s="18">
         <f t="shared" si="0"/>
@@ -2310,10 +2352,10 @@
       </c>
       <c r="P20" s="18"/>
       <c r="Q20" s="12" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="S20" s="12" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="21" spans="1:19" ht="48">
@@ -2324,10 +2366,10 @@
         <v>6</v>
       </c>
       <c r="C21" s="21" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="D21" s="15" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="E21" s="4" t="s">
         <v>48</v>
@@ -2336,13 +2378,13 @@
         <v>64</v>
       </c>
       <c r="G21" s="16" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="H21" s="17" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="I21" s="18" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="J21" s="18">
         <f t="shared" si="0"/>
@@ -2366,10 +2408,10 @@
       </c>
       <c r="P21" s="18"/>
       <c r="Q21" s="12" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="S21" s="12" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="22" spans="1:19" ht="36">
@@ -2380,10 +2422,10 @@
         <v>7</v>
       </c>
       <c r="C22" s="21" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="D22" s="15" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="E22" s="4" t="s">
         <v>49</v>
@@ -2392,13 +2434,13 @@
         <v>64</v>
       </c>
       <c r="G22" s="16" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="H22" s="17" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="I22" s="18" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="J22" s="18">
         <f t="shared" si="0"/>
@@ -2422,13 +2464,13 @@
       </c>
       <c r="P22" s="18"/>
       <c r="Q22" s="12" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="R22" s="12" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="S22" s="12" t="s">
-        <v>72</v>
+        <v>122</v>
       </c>
     </row>
     <row r="23" spans="1:19" ht="36">
@@ -2439,10 +2481,10 @@
         <v>7</v>
       </c>
       <c r="C23" s="21" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="D23" s="15" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="E23" s="4" t="s">
         <v>50</v>
@@ -2451,13 +2493,13 @@
         <v>64</v>
       </c>
       <c r="G23" s="16" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="H23" s="17" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="I23" s="18" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="J23" s="18">
         <f t="shared" si="0"/>
@@ -2481,10 +2523,10 @@
       </c>
       <c r="P23" s="18"/>
       <c r="Q23" s="12" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="S23" s="12" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="24" spans="1:19" ht="36">
@@ -2495,10 +2537,10 @@
         <v>7</v>
       </c>
       <c r="C24" s="21" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="D24" s="15" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="E24" s="4" t="s">
         <v>51</v>
@@ -2507,13 +2549,13 @@
         <v>64</v>
       </c>
       <c r="G24" s="16" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="H24" s="17" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="I24" s="18" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="J24" s="18">
         <f t="shared" si="0"/>
@@ -2537,10 +2579,10 @@
       </c>
       <c r="P24" s="18"/>
       <c r="Q24" s="12" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="S24" s="12" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="25" spans="1:19" ht="36">
@@ -2551,10 +2593,10 @@
         <v>7</v>
       </c>
       <c r="C25" s="21" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="D25" s="15" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="E25" s="4" t="s">
         <v>52</v>
@@ -2563,13 +2605,13 @@
         <v>64</v>
       </c>
       <c r="G25" s="16" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="H25" s="17" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="I25" s="18" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="J25" s="18">
         <f t="shared" si="0"/>
@@ -2593,10 +2635,10 @@
       </c>
       <c r="P25" s="18"/>
       <c r="Q25" s="12" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="S25" s="12" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="26" spans="1:19" ht="48">
@@ -2607,10 +2649,10 @@
         <v>8</v>
       </c>
       <c r="C26" s="21" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="D26" s="15" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="E26" s="4" t="s">
         <v>53</v>
@@ -2619,13 +2661,13 @@
         <v>64</v>
       </c>
       <c r="G26" s="16" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="H26" s="17" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="I26" s="18" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="J26" s="18">
         <f t="shared" si="0"/>
@@ -2649,13 +2691,13 @@
       </c>
       <c r="P26" s="18"/>
       <c r="Q26" s="12" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="R26" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="S26" s="12" t="s">
         <v>123</v>
-      </c>
-      <c r="S26" s="12" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="27" spans="1:19" ht="48">
@@ -2666,10 +2708,10 @@
         <v>8</v>
       </c>
       <c r="C27" s="21" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="D27" s="15" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="E27" s="4" t="s">
         <v>54</v>
@@ -2678,13 +2720,13 @@
         <v>64</v>
       </c>
       <c r="G27" s="16" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="H27" s="17" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="I27" s="18" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="J27" s="18">
         <f t="shared" si="0"/>
@@ -2708,10 +2750,10 @@
       </c>
       <c r="P27" s="18"/>
       <c r="Q27" s="12" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="S27" s="12" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="28" spans="1:19" ht="36">
@@ -2722,10 +2764,10 @@
         <v>8</v>
       </c>
       <c r="C28" s="21" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="D28" s="15" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="E28" s="4" t="s">
         <v>55</v>
@@ -2734,13 +2776,13 @@
         <v>64</v>
       </c>
       <c r="G28" s="16" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="H28" s="17" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="I28" s="18" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="J28" s="18">
         <f t="shared" si="0"/>
@@ -2764,10 +2806,10 @@
       </c>
       <c r="P28" s="18"/>
       <c r="Q28" s="12" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="S28" s="12" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="29" spans="1:19" ht="48">
@@ -2778,10 +2820,10 @@
         <v>9</v>
       </c>
       <c r="C29" s="21" t="s">
-        <v>116</v>
+        <v>105</v>
       </c>
       <c r="D29" s="15" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="E29" s="4" t="s">
         <v>56</v>
@@ -2790,13 +2832,13 @@
         <v>64</v>
       </c>
       <c r="G29" s="16" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="H29" s="17" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="I29" s="18" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="J29" s="18">
         <f t="shared" si="0"/>
@@ -2820,10 +2862,10 @@
       </c>
       <c r="P29" s="18"/>
       <c r="Q29" s="12" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="S29" s="12" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="30" spans="1:19" ht="24">
@@ -2834,10 +2876,10 @@
         <v>10</v>
       </c>
       <c r="C30" s="21" t="s">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="D30" s="15" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="E30" s="4" t="s">
         <v>57</v>
@@ -2846,13 +2888,13 @@
         <v>64</v>
       </c>
       <c r="G30" s="16" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="H30" s="17" t="s">
-        <v>105</v>
+        <v>94</v>
       </c>
       <c r="I30" s="18" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="J30" s="18">
         <f t="shared" si="0"/>
@@ -2876,13 +2918,13 @@
       </c>
       <c r="P30" s="18"/>
       <c r="Q30" s="12" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="R30" s="12" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="S30" s="12" t="s">
-        <v>74</v>
+        <v>124</v>
       </c>
     </row>
     <row r="31" spans="1:19" ht="60">
@@ -2893,10 +2935,10 @@
         <v>10</v>
       </c>
       <c r="C31" s="21" t="s">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="D31" s="15" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="E31" s="4" t="s">
         <v>58</v>
@@ -2905,13 +2947,13 @@
         <v>64</v>
       </c>
       <c r="G31" s="16" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="H31" s="17" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="I31" s="18" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="J31" s="18">
         <f t="shared" si="0"/>
@@ -2935,10 +2977,10 @@
       </c>
       <c r="P31" s="18"/>
       <c r="Q31" s="12" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="S31" s="12" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="32" spans="1:19" ht="36">
@@ -2949,10 +2991,10 @@
         <v>11</v>
       </c>
       <c r="C32" s="21" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="D32" s="15" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="E32" s="4" t="s">
         <v>59</v>
@@ -2961,13 +3003,13 @@
         <v>64</v>
       </c>
       <c r="G32" s="16" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="H32" s="17" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="I32" s="18" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="J32" s="18">
         <f t="shared" si="0"/>
@@ -2991,16 +3033,16 @@
       </c>
       <c r="P32" s="18"/>
       <c r="Q32" s="12" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="R32" s="12" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="S32" s="19" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="33" spans="1:19" ht="60">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="33" spans="1:22" ht="60">
       <c r="A33" s="13">
         <v>1032</v>
       </c>
@@ -3008,10 +3050,10 @@
         <v>11</v>
       </c>
       <c r="C33" s="21" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="D33" s="15" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="E33" s="4" t="s">
         <v>60</v>
@@ -3020,13 +3062,13 @@
         <v>64</v>
       </c>
       <c r="G33" s="16" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="H33" s="17" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="I33" s="18" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="J33" s="18">
         <f t="shared" si="0"/>
@@ -3050,13 +3092,13 @@
       </c>
       <c r="P33" s="18"/>
       <c r="Q33" s="12" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="S33" s="12" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="34" spans="1:19" ht="36">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="34" spans="1:22" ht="36">
       <c r="A34" s="13">
         <v>1033</v>
       </c>
@@ -3064,10 +3106,10 @@
         <v>11</v>
       </c>
       <c r="C34" s="21" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="D34" s="15" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="E34" s="4" t="s">
         <v>61</v>
@@ -3076,13 +3118,13 @@
         <v>64</v>
       </c>
       <c r="G34" s="16" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="H34" s="17" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="I34" s="18" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="J34" s="18">
         <f t="shared" si="0"/>
@@ -3106,13 +3148,13 @@
       </c>
       <c r="P34" s="18"/>
       <c r="Q34" s="12" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="S34" s="12" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="35" spans="1:19" ht="25.5">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="35" spans="1:22" ht="25.5">
       <c r="A35" s="13">
         <v>1034</v>
       </c>
@@ -3120,10 +3162,10 @@
         <v>12</v>
       </c>
       <c r="C35" s="21" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="D35" s="15" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="E35" s="4" t="s">
         <v>62</v>
@@ -3132,13 +3174,13 @@
         <v>64</v>
       </c>
       <c r="G35" s="16" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="H35" s="17" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="I35" s="18" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="J35" s="18">
         <f t="shared" si="0"/>
@@ -3162,16 +3204,16 @@
       </c>
       <c r="P35" s="18"/>
       <c r="Q35" s="12" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="R35" s="12" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="S35" s="12" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="36" spans="1:19" ht="60">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="36" spans="1:22" ht="48">
       <c r="A36" s="13">
         <v>1035</v>
       </c>
@@ -3179,10 +3221,10 @@
         <v>12</v>
       </c>
       <c r="C36" s="21" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="D36" s="15" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="E36" s="4" t="s">
         <v>63</v>
@@ -3191,13 +3233,13 @@
         <v>64</v>
       </c>
       <c r="G36" s="16" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="H36" s="17" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="I36" s="18" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="J36" s="18">
         <f t="shared" si="0"/>
@@ -3221,45 +3263,45 @@
       </c>
       <c r="P36" s="18"/>
       <c r="Q36" s="12" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="S36" s="12" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="37" spans="1:19" s="19" customFormat="1" ht="108">
-      <c r="A37" s="31">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="37" spans="1:22" s="19" customFormat="1" ht="15">
+      <c r="A37" s="30">
         <v>1036</v>
       </c>
       <c r="B37" s="19">
         <v>13</v>
       </c>
-      <c r="C37" s="32" t="s">
+      <c r="C37" s="33" t="s">
+        <v>131</v>
+      </c>
+      <c r="D37" s="31" t="s">
+        <v>115</v>
+      </c>
+      <c r="E37" s="34" t="s">
         <v>127</v>
       </c>
-      <c r="D37" s="33" t="s">
-        <v>126</v>
-      </c>
-      <c r="E37" s="34" t="s">
-        <v>128</v>
-      </c>
-      <c r="F37" s="37" t="s">
+      <c r="F37" s="33" t="s">
         <v>64</v>
       </c>
       <c r="G37" s="16" t="s">
-        <v>123</v>
-      </c>
-      <c r="H37" s="35" t="s">
-        <v>127</v>
-      </c>
-      <c r="I37" s="36" t="s">
-        <v>112</v>
-      </c>
-      <c r="J37" s="36">
+        <v>112</v>
+      </c>
+      <c r="H37" s="33" t="s">
+        <v>131</v>
+      </c>
+      <c r="I37" s="32" t="s">
+        <v>101</v>
+      </c>
+      <c r="J37" s="32">
         <f t="shared" si="0"/>
-        <v>309</v>
-      </c>
-      <c r="K37" s="36">
+        <v>42</v>
+      </c>
+      <c r="K37" s="32">
         <f t="shared" si="1"/>
         <v>13</v>
       </c>
@@ -3277,122 +3319,399 @@
       </c>
       <c r="P37" s="18"/>
       <c r="Q37" s="19" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="38" spans="1:19">
-      <c r="A38" s="13"/>
-      <c r="C38" s="21"/>
-      <c r="E38" s="28"/>
-      <c r="F38" s="16"/>
-      <c r="G38" s="16"/>
-      <c r="H38" s="17"/>
-      <c r="I38" s="18"/>
-      <c r="J38" s="18"/>
-      <c r="K38" s="18"/>
-      <c r="L38" s="18"/>
-      <c r="M38" s="18"/>
-      <c r="N38" s="18"/>
-      <c r="O38" s="18"/>
+        <v>101</v>
+      </c>
+      <c r="R37" s="19" t="s">
+        <v>101</v>
+      </c>
+      <c r="S37" s="12" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="38" spans="1:22" ht="30">
+      <c r="A38" s="13">
+        <v>1037</v>
+      </c>
+      <c r="B38" s="12">
+        <v>14</v>
+      </c>
+      <c r="C38" s="33" t="s">
+        <v>132</v>
+      </c>
+      <c r="D38" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="E38" s="34" t="s">
+        <v>129</v>
+      </c>
+      <c r="F38" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="G38" s="16" t="s">
+        <v>112</v>
+      </c>
+      <c r="H38" s="33" t="s">
+        <v>132</v>
+      </c>
+      <c r="I38" s="18" t="s">
+        <v>101</v>
+      </c>
+      <c r="J38" s="32">
+        <f t="shared" si="0"/>
+        <v>49</v>
+      </c>
+      <c r="K38" s="18">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="L38" s="18">
+        <v>1</v>
+      </c>
+      <c r="M38" s="18">
+        <v>0</v>
+      </c>
+      <c r="N38" s="18">
+        <v>0</v>
+      </c>
+      <c r="O38" s="18">
+        <v>0</v>
+      </c>
       <c r="P38" s="18"/>
-    </row>
-    <row r="39" spans="1:19">
-      <c r="A39" s="13"/>
-      <c r="C39" s="21"/>
-      <c r="E39" s="28"/>
-      <c r="F39" s="16"/>
-      <c r="G39" s="16"/>
-      <c r="H39" s="17"/>
-      <c r="I39" s="18"/>
-      <c r="J39" s="18"/>
-      <c r="K39" s="18"/>
-      <c r="L39" s="18"/>
-      <c r="M39" s="18"/>
-      <c r="N39" s="18"/>
-      <c r="O39" s="18"/>
+      <c r="Q38" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="R38" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="S38" s="12" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="39" spans="1:22" ht="25.5">
+      <c r="A39" s="13">
+        <v>1038</v>
+      </c>
+      <c r="B39" s="12">
+        <v>15</v>
+      </c>
+      <c r="C39" s="33" t="s">
+        <v>133</v>
+      </c>
+      <c r="D39" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="E39" s="35" t="s">
+        <v>134</v>
+      </c>
+      <c r="F39" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="G39" s="16" t="s">
+        <v>112</v>
+      </c>
+      <c r="H39" s="33" t="s">
+        <v>140</v>
+      </c>
+      <c r="I39" s="18" t="s">
+        <v>101</v>
+      </c>
+      <c r="J39" s="32">
+        <f t="shared" si="0"/>
+        <v>76</v>
+      </c>
+      <c r="K39" s="18">
+        <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+      <c r="L39" s="18">
+        <v>1</v>
+      </c>
+      <c r="M39" s="18">
+        <v>0</v>
+      </c>
+      <c r="N39" s="18">
+        <v>0</v>
+      </c>
+      <c r="O39" s="18">
+        <v>0</v>
+      </c>
       <c r="P39" s="18"/>
-    </row>
-    <row r="40" spans="1:19">
-      <c r="A40" s="13"/>
-      <c r="C40" s="21"/>
-      <c r="E40" s="28"/>
-      <c r="F40" s="16"/>
-      <c r="G40" s="16"/>
-      <c r="H40" s="17"/>
-      <c r="I40" s="18"/>
-      <c r="J40" s="18"/>
-      <c r="K40" s="18"/>
-      <c r="L40" s="18"/>
-      <c r="M40" s="18"/>
-      <c r="N40" s="18"/>
-      <c r="O40" s="18"/>
+      <c r="Q39" s="12" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="40" spans="1:22">
+      <c r="A40" s="13">
+        <v>1039</v>
+      </c>
+      <c r="B40" s="12">
+        <v>15</v>
+      </c>
+      <c r="C40" s="33" t="s">
+        <v>133</v>
+      </c>
+      <c r="D40" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="E40" s="35" t="s">
+        <v>135</v>
+      </c>
+      <c r="F40" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="G40" s="16" t="s">
+        <v>112</v>
+      </c>
+      <c r="H40" s="33" t="s">
+        <v>141</v>
+      </c>
+      <c r="I40" s="18" t="s">
+        <v>101</v>
+      </c>
+      <c r="J40" s="32">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="K40" s="18">
+        <f t="shared" si="1"/>
+        <v>17</v>
+      </c>
+      <c r="L40" s="18">
+        <v>1</v>
+      </c>
+      <c r="M40" s="18">
+        <v>0</v>
+      </c>
+      <c r="N40" s="18">
+        <v>0</v>
+      </c>
+      <c r="O40" s="18">
+        <v>0</v>
+      </c>
       <c r="P40" s="18"/>
-    </row>
-    <row r="41" spans="1:19">
-      <c r="A41" s="13"/>
-      <c r="C41" s="21"/>
-      <c r="E41" s="28"/>
-      <c r="F41" s="16"/>
-      <c r="G41" s="16"/>
-      <c r="H41" s="17"/>
-      <c r="I41" s="18"/>
-      <c r="J41" s="18"/>
-      <c r="K41" s="18"/>
-      <c r="L41" s="18"/>
-      <c r="M41" s="18"/>
-      <c r="N41" s="18"/>
-      <c r="O41" s="18"/>
+      <c r="Q40" s="12" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="41" spans="1:22">
+      <c r="A41" s="13">
+        <v>1040</v>
+      </c>
+      <c r="B41" s="12">
+        <v>15</v>
+      </c>
+      <c r="C41" s="33" t="s">
+        <v>133</v>
+      </c>
+      <c r="D41" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="E41" s="35" t="s">
+        <v>136</v>
+      </c>
+      <c r="F41" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="G41" s="16" t="s">
+        <v>112</v>
+      </c>
+      <c r="H41" s="33" t="s">
+        <v>142</v>
+      </c>
+      <c r="I41" s="18" t="s">
+        <v>101</v>
+      </c>
+      <c r="J41" s="32">
+        <f t="shared" ref="J41:J44" si="2">LEN(E41)</f>
+        <v>12</v>
+      </c>
+      <c r="K41" s="18">
+        <f t="shared" ref="K41:K44" si="3">LEN(H41)</f>
+        <v>10</v>
+      </c>
+      <c r="L41" s="18">
+        <v>1</v>
+      </c>
+      <c r="M41" s="18">
+        <v>0</v>
+      </c>
+      <c r="N41" s="18">
+        <v>0</v>
+      </c>
+      <c r="O41" s="18">
+        <v>0</v>
+      </c>
       <c r="P41" s="18"/>
-    </row>
-    <row r="42" spans="1:19">
-      <c r="A42" s="13"/>
-      <c r="C42" s="21"/>
-      <c r="E42" s="28"/>
-      <c r="F42" s="16"/>
-      <c r="G42" s="16"/>
-      <c r="H42" s="17"/>
-      <c r="I42" s="18"/>
-      <c r="J42" s="18"/>
-      <c r="K42" s="18"/>
-      <c r="L42" s="18"/>
-      <c r="M42" s="18"/>
-      <c r="N42" s="18"/>
-      <c r="O42" s="18"/>
+      <c r="Q41" s="12" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="42" spans="1:22">
+      <c r="A42" s="13">
+        <v>1041</v>
+      </c>
+      <c r="B42" s="12">
+        <v>15</v>
+      </c>
+      <c r="C42" s="33" t="s">
+        <v>133</v>
+      </c>
+      <c r="D42" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="E42" s="35" t="s">
+        <v>137</v>
+      </c>
+      <c r="F42" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="G42" s="16" t="s">
+        <v>112</v>
+      </c>
+      <c r="H42" s="33" t="s">
+        <v>143</v>
+      </c>
+      <c r="I42" s="18" t="s">
+        <v>101</v>
+      </c>
+      <c r="J42" s="32">
+        <f t="shared" si="2"/>
+        <v>23</v>
+      </c>
+      <c r="K42" s="18">
+        <f t="shared" si="3"/>
+        <v>20</v>
+      </c>
+      <c r="L42" s="18">
+        <v>1</v>
+      </c>
+      <c r="M42" s="18">
+        <v>0</v>
+      </c>
+      <c r="N42" s="18">
+        <v>0</v>
+      </c>
+      <c r="O42" s="18">
+        <v>0</v>
+      </c>
       <c r="P42" s="18"/>
-    </row>
-    <row r="43" spans="1:19">
-      <c r="A43" s="13"/>
-      <c r="C43" s="21"/>
-      <c r="E43" s="28"/>
-      <c r="F43" s="16"/>
-      <c r="G43" s="16"/>
-      <c r="H43" s="17"/>
-      <c r="I43" s="18"/>
-      <c r="J43" s="18"/>
-      <c r="K43" s="18"/>
-      <c r="L43" s="18"/>
-      <c r="M43" s="18"/>
-      <c r="N43" s="18"/>
-      <c r="O43" s="18"/>
+      <c r="Q42" s="12" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="43" spans="1:22" ht="25.5">
+      <c r="A43" s="13">
+        <v>1042</v>
+      </c>
+      <c r="B43" s="12">
+        <v>15</v>
+      </c>
+      <c r="C43" s="33" t="s">
+        <v>133</v>
+      </c>
+      <c r="D43" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="E43" s="35" t="s">
+        <v>138</v>
+      </c>
+      <c r="F43" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="G43" s="16" t="s">
+        <v>112</v>
+      </c>
+      <c r="H43" s="33" t="s">
+        <v>144</v>
+      </c>
+      <c r="I43" s="18" t="s">
+        <v>101</v>
+      </c>
+      <c r="J43" s="32">
+        <f t="shared" si="2"/>
+        <v>44</v>
+      </c>
+      <c r="K43" s="18">
+        <f t="shared" si="3"/>
+        <v>14</v>
+      </c>
+      <c r="L43" s="18">
+        <v>1</v>
+      </c>
+      <c r="M43" s="18">
+        <v>0</v>
+      </c>
+      <c r="N43" s="18">
+        <v>0</v>
+      </c>
+      <c r="O43" s="18">
+        <v>0</v>
+      </c>
       <c r="P43" s="18"/>
-    </row>
-    <row r="44" spans="1:19">
-      <c r="A44" s="13"/>
-      <c r="C44" s="21"/>
-      <c r="E44" s="3"/>
-      <c r="F44" s="16"/>
-      <c r="G44" s="16"/>
-      <c r="H44" s="17"/>
-      <c r="I44" s="18"/>
-      <c r="J44" s="18"/>
-      <c r="K44" s="18"/>
-      <c r="L44" s="18"/>
-      <c r="M44" s="18"/>
-      <c r="N44" s="18"/>
-      <c r="O44" s="18"/>
+      <c r="Q43" s="12" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="44" spans="1:22">
+      <c r="A44" s="13">
+        <v>1043</v>
+      </c>
+      <c r="B44" s="12">
+        <v>15</v>
+      </c>
+      <c r="C44" s="33" t="s">
+        <v>133</v>
+      </c>
+      <c r="D44" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="E44" s="35" t="s">
+        <v>139</v>
+      </c>
+      <c r="F44" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="G44" s="16" t="s">
+        <v>101</v>
+      </c>
+      <c r="H44" s="33" t="s">
+        <v>145</v>
+      </c>
+      <c r="I44" s="18" t="s">
+        <v>101</v>
+      </c>
+      <c r="J44" s="32">
+        <f t="shared" si="2"/>
+        <v>6</v>
+      </c>
+      <c r="K44" s="18">
+        <f t="shared" si="3"/>
+        <v>5</v>
+      </c>
+      <c r="L44" s="18">
+        <v>1</v>
+      </c>
+      <c r="M44" s="18">
+        <v>0</v>
+      </c>
+      <c r="N44" s="18">
+        <v>0</v>
+      </c>
+      <c r="O44" s="18">
+        <v>0</v>
+      </c>
       <c r="P44" s="18"/>
-    </row>
-    <row r="45" spans="1:19">
+      <c r="Q44" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="T44" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="V44" s="12">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="1:22">
       <c r="A45" s="13"/>
       <c r="C45" s="21"/>
       <c r="E45" s="3"/>
@@ -3408,7 +3727,7 @@
       <c r="O45" s="18"/>
       <c r="P45" s="18"/>
     </row>
-    <row r="46" spans="1:19">
+    <row r="46" spans="1:22">
       <c r="A46" s="13"/>
       <c r="C46" s="21"/>
       <c r="E46" s="3"/>
@@ -3424,7 +3743,7 @@
       <c r="O46" s="18"/>
       <c r="P46" s="18"/>
     </row>
-    <row r="47" spans="1:19">
+    <row r="47" spans="1:22">
       <c r="A47" s="13"/>
       <c r="C47" s="21"/>
       <c r="E47" s="5"/>
@@ -3440,7 +3759,7 @@
       <c r="O47" s="18"/>
       <c r="P47" s="18"/>
     </row>
-    <row r="48" spans="1:19" ht="13.5" thickBot="1">
+    <row r="48" spans="1:22" ht="13.5" thickBot="1">
       <c r="A48" s="13"/>
       <c r="C48" s="21"/>
       <c r="E48" s="6"/>
